--- a/data/trans_dic/P02E$contratada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,71</t>
+          <t>0,71; 6,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,36</t>
+          <t>0,56; 5,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,98</t>
+          <t>0,63; 5,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,51</t>
+          <t>1,08; 6,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,42</t>
+          <t>1,12; 4,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,72</t>
+          <t>0,66; 5,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,84</t>
+          <t>1,35; 4,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,86</t>
+          <t>1,3; 3,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,63</t>
+          <t>0,99; 4,93</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,24</t>
+          <t>0,23; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,07</t>
+          <t>1,25; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,54</t>
+          <t>0,41; 2,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,0</t>
+          <t>0,46; 1,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,04</t>
+          <t>0,44; 2,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,16</t>
+          <t>0,49; 2,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,4</t>
+          <t>0,46; 1,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,43</t>
+          <t>0,95; 2,5</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,2</t>
+          <t>0,7; 7,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 11,1</t>
+          <t>2,65; 11,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,12</t>
+          <t>0,69; 5,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,01</t>
+          <t>0,64; 6,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,56</t>
+          <t>2,09; 8,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,63</t>
+          <t>2,44; 8,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,15</t>
+          <t>1,28; 4,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,03</t>
+          <t>2,69; 7,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,33</t>
+          <t>2,08; 6,28</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,23</t>
+          <t>0,85; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,82</t>
+          <t>0,93; 2,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,72</t>
+          <t>1,41; 3,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>1,04; 2,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,78</t>
+          <t>1,26; 2,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,07</t>
+          <t>1,28; 3,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,57</t>
+          <t>1,16; 2,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,42</t>
+          <t>1,33; 2,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,92</t>
+          <t>1,56; 2,9</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>826; 7605</t>
+          <t>800; 7835</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1079; 9708</t>
+          <t>1008; 9703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>801; 7633</t>
+          <t>800; 7566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2906; 14939</t>
+          <t>2932; 16258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4107; 17147</t>
+          <t>4331; 17857</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1301; 11313</t>
+          <t>1300; 11059</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4435; 18616</t>
+          <t>5201; 18737</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6899; 21973</t>
+          <t>7382; 22658</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3171; 15070</t>
+          <t>3233; 16041</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>899; 12517</t>
+          <t>900; 12620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>936; 8034</t>
+          <t>934; 8093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5865; 19544</t>
+          <t>6008; 22329</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2327; 14461</t>
+          <t>2325; 14013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4805; 18138</t>
+          <t>4124; 17581</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3040; 14202</t>
+          <t>3083; 14342</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5337; 20609</t>
+          <t>4691; 20185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6852; 21418</t>
+          <t>7085; 22702</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11485; 28634</t>
+          <t>11147; 29486</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1021; 9094</t>
+          <t>884; 9266</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4811; 19652</t>
+          <t>4692; 20165</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>979; 8843</t>
+          <t>991; 8627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1001; 9995</t>
+          <t>1062; 10414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3994; 19152</t>
+          <t>4688; 18890</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5085; 18428</t>
+          <t>5218; 18648</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3651; 15066</t>
+          <t>3749; 13967</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11523; 32188</t>
+          <t>10794; 30291</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7623; 22679</t>
+          <t>7431; 22495</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5288; 20210</t>
+          <t>5347; 19648</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9946; 27701</t>
+          <t>9135; 28034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10613; 27992</t>
+          <t>10612; 28057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9755; 28288</t>
+          <t>10421; 28616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18523; 42096</t>
+          <t>19166; 41051</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14020; 34084</t>
+          <t>14144; 33967</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17969; 41980</t>
+          <t>18906; 41571</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33039; 60461</t>
+          <t>33266; 61871</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29224; 54368</t>
+          <t>29123; 53971</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,92</t>
+          <t>0,71; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,36</t>
+          <t>0,55; 5,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,93</t>
+          <t>0,63; 5,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,0</t>
+          <t>1,19; 5,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,6</t>
+          <t>1,08; 4,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,59</t>
+          <t>0,66; 5,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,87</t>
+          <t>1,29; 4,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,98</t>
+          <t>1,26; 3,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,93</t>
+          <t>1,0; 4,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,26</t>
+          <t>0,24; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,29</t>
+          <t>0,15; 1,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,65</t>
+          <t>1,31; 4,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,47</t>
+          <t>0,41; 2,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,94</t>
+          <t>0,57; 2,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,06</t>
+          <t>0,45; 1,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,11</t>
+          <t>0,51; 2,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,48</t>
+          <t>0,46; 1,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,5</t>
+          <t>1,03; 2,56</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,34</t>
+          <t>0,82; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,39</t>
+          <t>2,64; 10,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,97</t>
+          <t>0,69; 5,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,26</t>
+          <t>0,61; 6,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,44</t>
+          <t>1,7; 7,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,73</t>
+          <t>2,36; 8,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,77</t>
+          <t>1,07; 5,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,56</t>
+          <t>2,85; 7,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,28</t>
+          <t>2,01; 6,37</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,14</t>
+          <t>0,92; 3,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,85</t>
+          <t>0,99; 2,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,73</t>
+          <t>1,35; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,85</t>
+          <t>0,99; 2,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,71</t>
+          <t>1,25; 2,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,06</t>
+          <t>1,25; 2,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,55</t>
+          <t>1,19; 2,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,47</t>
+          <t>1,32; 2,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,9</t>
+          <t>1,53; 2,91</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>800; 7835</t>
+          <t>807; 7820</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1008; 9703</t>
+          <t>994; 9868</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>800; 7566</t>
+          <t>802; 7380</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2932; 16258</t>
+          <t>3219; 15418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4331; 17857</t>
+          <t>4181; 17017</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1300; 11059</t>
+          <t>1309; 11555</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5201; 18737</t>
+          <t>4942; 18839</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7382; 22658</t>
+          <t>7163; 22341</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3233; 16041</t>
+          <t>3262; 15196</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>900; 12620</t>
+          <t>912; 12556</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>934; 8093</t>
+          <t>938; 8098</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6008; 22329</t>
+          <t>6305; 20545</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2325; 14013</t>
+          <t>2323; 13825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4124; 17581</t>
+          <t>5191; 18504</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3083; 14342</t>
+          <t>3106; 13471</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4691; 20185</t>
+          <t>4884; 22137</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7085; 22702</t>
+          <t>7084; 22988</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11147; 29486</t>
+          <t>12128; 30175</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>884; 9266</t>
+          <t>1035; 9473</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4692; 20165</t>
+          <t>4670; 19304</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>991; 8627</t>
+          <t>997; 8504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1062; 10414</t>
+          <t>1019; 10373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4688; 18890</t>
+          <t>3809; 17684</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5218; 18648</t>
+          <t>5030; 18439</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3749; 13967</t>
+          <t>3130; 14716</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10794; 30291</t>
+          <t>11440; 31123</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7431; 22495</t>
+          <t>7200; 22814</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5347; 19648</t>
+          <t>5776; 21178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9135; 28034</t>
+          <t>9692; 27310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10612; 28057</t>
+          <t>10189; 27932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10421; 28616</t>
+          <t>9967; 28037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19166; 41051</t>
+          <t>19027; 41013</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14144; 33967</t>
+          <t>13833; 33200</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18906; 41571</t>
+          <t>19499; 43188</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33266; 61871</t>
+          <t>33028; 62350</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29123; 53971</t>
+          <t>28385; 54078</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
